--- a/examples/进销存台账模板.xlsx
+++ b/examples/进销存台账模板.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>cf7d27cdcdd2</t>
+          <t>e2a9b9a24b3f</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -583,7 +583,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-27 17:27:30</t>
+          <t>2026-10-27 17:44:54</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -819,7 +819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -861,6 +861,48 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>OP-000001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-10-27 17:44:54</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>init</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>初始化台账 公司名称(待填) 起始期间 2026-01</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>创建工作表与元数据</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>examples/进销存台账模板.xlsx</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>成功</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1044,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-27 17:27:30</t>
+          <t>2026-10-27 17:44:54</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
